--- a/SeaAroundUsExtraction/eez_output/regional_calculations/EEZ_918_France_Mediterranean.xlsx
+++ b/SeaAroundUsExtraction/eez_output/regional_calculations/EEZ_918_France_Mediterranean.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Species" sheetId="1" r:id="R7eae0405a69a484a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Commercial" sheetId="2" r:id="Rc5820b9f00e44fda"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="3" r:id="Rca42570faa034d63"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missing TL" sheetId="4" r:id="Rb22695ccfa354574"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="5" r:id="R88840701ce534437"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadata" sheetId="6" r:id="R9b0edaae137344d5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Species" sheetId="1" r:id="R8d1a792656714e07"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Commercial" sheetId="2" r:id="R1b2438a732c54a22"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="3" r:id="Rc109ccb3bfb84284"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missing TL" sheetId="4" r:id="Re012399421dd4d01"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="5" r:id="R48b98c9e38804f2b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadata" sheetId="6" r:id="R3ad31bb0258d4822"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -18,13 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="6">
+  <x:numFmts count="4">
     <x:numFmt numFmtId="200" formatCode="0"/>
     <x:numFmt numFmtId="201" formatCode="#,##0.00"/>
     <x:numFmt numFmtId="202" formatCode="0.0000"/>
-    <x:numFmt numFmtId="203" formatCode="#,##0"/>
-    <x:numFmt numFmtId="204" formatCode="0.00%"/>
-    <x:numFmt numFmtId="205" formatCode="0.00"/>
+    <x:numFmt numFmtId="203" formatCode="0.00"/>
   </x:numFmts>
   <x:fonts count="7">
     <x:font>
@@ -184,7 +182,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="37">
+  <x:cellXfs count="35">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <x:extLst>
@@ -244,8 +242,6 @@
     <x:xf numFmtId="200" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="201" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="202" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="203" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="204" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <x:extLst>
         <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
@@ -253,14 +249,14 @@
         </x:ext>
       </x:extLst>
     </x:xf>
-    <x:xf numFmtId="205" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="203" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
   </x:cellStyles>
-  <x:dxfs count="3">
+  <x:dxfs count="1">
     <x:dxf>
       <x:font>
         <x:color rgb="FF9A3412"/>
@@ -268,28 +264,6 @@
       <x:fill>
         <x:patternFill patternType="solid">
           <x:bgColor rgb="FFFCEAD8"/>
-        </x:patternFill>
-      </x:fill>
-    </x:dxf>
-    <x:dxf>
-      <x:font>
-        <x:b/>
-        <x:color rgb="FFB42318"/>
-      </x:font>
-      <x:fill>
-        <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFFEE4E2"/>
-        </x:patternFill>
-      </x:fill>
-    </x:dxf>
-    <x:dxf>
-      <x:font>
-        <x:b/>
-        <x:color rgb="FFB42318"/>
-      </x:font>
-      <x:fill>
-        <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFFEE4E2"/>
         </x:patternFill>
       </x:fill>
     </x:dxf>
@@ -345,56 +319,36 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="EEZ918CommercialTable" displayName="EEZ918CommercialTable" ref="A1:O13" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:O13"/>
-  <x:tableColumns count="15">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="EEZ918CommercialTable" displayName="EEZ918CommercialTable" ref="A1:E13" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:E13"/>
+  <x:tableColumns count="5">
     <x:tableColumn id="1" name="commercial_group"/>
-    <x:tableColumn id="2" name="taxon_count_total"/>
-    <x:tableColumn id="3" name="taxon_count_matched"/>
-    <x:tableColumn id="4" name="catch_tonnes_total"/>
-    <x:tableColumn id="5" name="catch_tonnes_matched"/>
-    <x:tableColumn id="6" name="catch_tonnes_missing_tl"/>
-    <x:tableColumn id="7" name="catch_coverage_fraction"/>
-    <x:tableColumn id="8" name="sppr_correct"/>
-    <x:tableColumn id="9" name="ppr_correct"/>
-    <x:tableColumn id="10" name="tl_weighted_jensen"/>
-    <x:tableColumn id="11" name="sppr_jensen"/>
-    <x:tableColumn id="12" name="ppr_jensen"/>
-    <x:tableColumn id="13" name="jensen_difference"/>
-    <x:tableColumn id="14" name="jensen_ratio_correct_to_error"/>
-    <x:tableColumn id="15" name="jensen_percent_difference"/>
+    <x:tableColumn id="2" name="catch_tonnes_matched"/>
+    <x:tableColumn id="3" name="tl_weighted"/>
+    <x:tableColumn id="4" name="sppr"/>
+    <x:tableColumn id="5" name="ppr"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="EEZ918FunctionalTable" displayName="EEZ918FunctionalTable" ref="A1:O26" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:O26"/>
-  <x:tableColumns count="15">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="EEZ918FunctionalTable" displayName="EEZ918FunctionalTable" ref="A1:E26" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:E26"/>
+  <x:tableColumns count="5">
     <x:tableColumn id="1" name="functional_group"/>
-    <x:tableColumn id="2" name="taxon_count_total"/>
-    <x:tableColumn id="3" name="taxon_count_matched"/>
-    <x:tableColumn id="4" name="catch_tonnes_total"/>
-    <x:tableColumn id="5" name="catch_tonnes_matched"/>
-    <x:tableColumn id="6" name="catch_tonnes_missing_tl"/>
-    <x:tableColumn id="7" name="catch_coverage_fraction"/>
-    <x:tableColumn id="8" name="sppr_correct"/>
-    <x:tableColumn id="9" name="ppr_correct"/>
-    <x:tableColumn id="10" name="tl_weighted_jensen"/>
-    <x:tableColumn id="11" name="sppr_jensen"/>
-    <x:tableColumn id="12" name="ppr_jensen"/>
-    <x:tableColumn id="13" name="jensen_difference"/>
-    <x:tableColumn id="14" name="jensen_ratio_correct_to_error"/>
-    <x:tableColumn id="15" name="jensen_percent_difference"/>
+    <x:tableColumn id="2" name="catch_tonnes_matched"/>
+    <x:tableColumn id="3" name="tl_weighted"/>
+    <x:tableColumn id="4" name="sppr"/>
+    <x:tableColumn id="5" name="ppr"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="EEZ918ValidationTable" displayName="EEZ918ValidationTable" ref="A1:D19" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:D19"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="EEZ918ValidationTable" displayName="EEZ918ValidationTable" ref="A1:D17" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:D17"/>
   <x:tableColumns count="4">
     <x:tableColumn id="1" name="unit_id"/>
     <x:tableColumn id="2" name="check"/>
@@ -11347,7 +11301,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9cba7652b46c40cf"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R30ef91a7ff7d4b4d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11357,20 +11311,10 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="26" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="15" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="15" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="16" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
@@ -11378,714 +11322,250 @@
         <x:v>commercial_group</x:v>
       </x:c>
       <x:c r="B1" s="29" t="str">
-        <x:v>taxon_count_total</x:v>
+        <x:v>catch_tonnes_matched</x:v>
       </x:c>
       <x:c r="C1" s="29" t="str">
-        <x:v>taxon_count_matched</x:v>
+        <x:v>tl_weighted</x:v>
       </x:c>
       <x:c r="D1" s="29" t="str">
-        <x:v>catch_tonnes_total</x:v>
+        <x:v>sppr</x:v>
       </x:c>
       <x:c r="E1" s="29" t="str">
-        <x:v>catch_tonnes_matched</x:v>
-      </x:c>
-      <x:c r="F1" s="29" t="str">
-        <x:v>catch_tonnes_missing_tl</x:v>
-      </x:c>
-      <x:c r="G1" s="29" t="str">
-        <x:v>catch_coverage_fraction</x:v>
-      </x:c>
-      <x:c r="H1" s="29" t="str">
-        <x:v>sppr_correct</x:v>
-      </x:c>
-      <x:c r="I1" s="29" t="str">
-        <x:v>ppr_correct</x:v>
-      </x:c>
-      <x:c r="J1" s="29" t="str">
-        <x:v>tl_weighted_jensen</x:v>
-      </x:c>
-      <x:c r="K1" s="29" t="str">
-        <x:v>sppr_jensen</x:v>
-      </x:c>
-      <x:c r="L1" s="29" t="str">
-        <x:v>ppr_jensen</x:v>
-      </x:c>
-      <x:c r="M1" s="29" t="str">
-        <x:v>jensen_difference</x:v>
-      </x:c>
-      <x:c r="N1" s="29" t="str">
-        <x:v>jensen_ratio_correct_to_error</x:v>
-      </x:c>
-      <x:c r="O1" s="29" t="str">
-        <x:v>jensen_percent_difference</x:v>
+        <x:v>ppr</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="18" customHeight="1">
       <x:c r="A2" s="24" t="str">
         <x:v>Anchovies</x:v>
       </x:c>
-      <x:c r="B2" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C2" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D2" s="31" t="n">
+      <x:c r="B2" s="31" t="n">
         <x:v>4130.6810922012</x:v>
       </x:c>
+      <x:c r="C2" s="32" t="n">
+        <x:v>3.11</x:v>
+      </x:c>
+      <x:c r="D2" s="32" t="n">
+        <x:f>IF(C2="","",(1/'Metadata'!$B$5)^(C2-1))</x:f>
+        <x:v>128.82495516931337</x:v>
+      </x:c>
       <x:c r="E2" s="31" t="n">
-        <x:v>4130.6810922012</x:v>
-      </x:c>
-      <x:c r="F2" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G2" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H2" s="32" t="n">
-        <x:f>IF(E2=0,"",I2/E2)</x:f>
-        <x:v>128.82495516931337</x:v>
-      </x:c>
-      <x:c r="I2" s="31" t="n">
-        <x:f>IF(C2=0,"",SUMIF('Species'!$H$2:$H$160,A2,'Species'!$U$2:$U$160))</x:f>
+        <x:f>IF(B2=0,"",B2*D2)</x:f>
         <x:v>532134.8065215499</x:v>
-      </x:c>
-      <x:c r="J2" s="32" t="n">
-        <x:v>3.11</x:v>
-      </x:c>
-      <x:c r="K2" s="32" t="n">
-        <x:f>IF(J2="","",(1/'Metadata'!$B$5)^(J2-1))</x:f>
-        <x:v>128.82495516931337</x:v>
-      </x:c>
-      <x:c r="L2" s="31" t="n">
-        <x:f>IF(E2=0,"",E2*K2)</x:f>
-        <x:v>532134.8065215499</x:v>
-      </x:c>
-      <x:c r="M2" s="31" t="n">
-        <x:f>IF(E2=0,"",I2-L2)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N2" s="32" t="n">
-        <x:f>IF(L2=0,"",I2/L2)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O2" s="34" t="n">
-        <x:f>IF(L2=0,"",M2/L2)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="18" customHeight="1">
       <x:c r="A3" s="24" t="str">
         <x:v>Cod-likes</x:v>
       </x:c>
-      <x:c r="B3" s="33" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="C3" s="33" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="D3" s="31" t="n">
+      <x:c r="B3" s="31" t="n">
         <x:v>7116.351371625101</x:v>
       </x:c>
+      <x:c r="C3" s="32" t="n">
+        <x:v>4.124252987364108</x:v>
+      </x:c>
+      <x:c r="D3" s="32" t="n">
+        <x:f>IF(C3="","",(1/'Metadata'!$B$5)^(C3-1))</x:f>
+        <x:v>1331.2296666281088</x:v>
+      </x:c>
       <x:c r="E3" s="31" t="n">
-        <x:v>7116.351371625101</x:v>
-      </x:c>
-      <x:c r="F3" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G3" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H3" s="32" t="n">
-        <x:f>IF(E3=0,"",I3/E3)</x:f>
-        <x:v>1692.6707080121562</x:v>
-      </x:c>
-      <x:c r="I3" s="31" t="n">
-        <x:f>IF(C3=0,"",SUMIF('Species'!$H$2:$H$160,A3,'Species'!$U$2:$U$160))</x:f>
-        <x:v>12045639.514671938</x:v>
-      </x:c>
-      <x:c r="J3" s="32" t="n">
-        <x:v>4.124252987364108</x:v>
-      </x:c>
-      <x:c r="K3" s="32" t="n">
-        <x:f>IF(J3="","",(1/'Metadata'!$B$5)^(J3-1))</x:f>
-        <x:v>1331.2296666281088</x:v>
-      </x:c>
-      <x:c r="L3" s="31" t="n">
-        <x:f>IF(E3=0,"",E3*K3)</x:f>
+        <x:f>IF(B3=0,"",B3*D3)</x:f>
         <x:v>9473498.064056968</x:v>
-      </x:c>
-      <x:c r="M3" s="31" t="n">
-        <x:f>IF(E3=0,"",I3-L3)</x:f>
-        <x:v>2572141.45061497</x:v>
-      </x:c>
-      <x:c r="N3" s="32" t="n">
-        <x:f>IF(L3=0,"",I3/L3)</x:f>
-        <x:v>1.2715091546145803</x:v>
-      </x:c>
-      <x:c r="O3" s="34" t="n">
-        <x:f>IF(L3=0,"",M3/L3)</x:f>
-        <x:v>0.27150915461458025</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="18" customHeight="1">
       <x:c r="A4" s="24" t="str">
         <x:v>Crustaceans</x:v>
       </x:c>
-      <x:c r="B4" s="33" t="n">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="C4" s="33" t="n">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="D4" s="31" t="n">
+      <x:c r="B4" s="31" t="n">
         <x:v>538.0510175575</x:v>
       </x:c>
+      <x:c r="C4" s="32" t="n">
+        <x:v>3.1541520382635118</x:v>
+      </x:c>
+      <x:c r="D4" s="32" t="n">
+        <x:f>IF(C4="","",(1/'Metadata'!$B$5)^(C4-1))</x:f>
+        <x:v>142.6106759159044</x:v>
+      </x:c>
       <x:c r="E4" s="31" t="n">
-        <x:v>538.0510175575</x:v>
-      </x:c>
-      <x:c r="F4" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G4" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H4" s="32" t="n">
-        <x:f>IF(E4=0,"",I4/E4)</x:f>
-        <x:v>208.43582601985787</x:v>
-      </x:c>
-      <x:c r="I4" s="31" t="n">
-        <x:f>IF(C4=0,"",SUMIF('Species'!$H$2:$H$160,A4,'Species'!$U$2:$U$160))</x:f>
-        <x:v>112149.10828542257</x:v>
-      </x:c>
-      <x:c r="J4" s="32" t="n">
-        <x:v>3.1541520382635118</x:v>
-      </x:c>
-      <x:c r="K4" s="32" t="n">
-        <x:f>IF(J4="","",(1/'Metadata'!$B$5)^(J4-1))</x:f>
-        <x:v>142.6106759159044</x:v>
-      </x:c>
-      <x:c r="L4" s="31" t="n">
-        <x:f>IF(E4=0,"",E4*K4)</x:f>
+        <x:f>IF(B4=0,"",B4*D4)</x:f>
         <x:v>76731.81929111523</x:v>
-      </x:c>
-      <x:c r="M4" s="31" t="n">
-        <x:f>IF(E4=0,"",I4-L4)</x:f>
-        <x:v>35417.28899430734</x:v>
-      </x:c>
-      <x:c r="N4" s="32" t="n">
-        <x:f>IF(L4=0,"",I4/L4)</x:f>
-        <x:v>1.4615723870684805</x:v>
-      </x:c>
-      <x:c r="O4" s="34" t="n">
-        <x:f>IF(L4=0,"",M4/L4)</x:f>
-        <x:v>0.4615723870684805</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="18" customHeight="1">
       <x:c r="A5" s="24" t="str">
         <x:v>Flatfishes</x:v>
       </x:c>
-      <x:c r="B5" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="C5" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="D5" s="31" t="n">
+      <x:c r="B5" s="31" t="n">
         <x:v>733.6327273358</x:v>
       </x:c>
+      <x:c r="C5" s="32" t="n">
+        <x:v>3.633944635497567</x:v>
+      </x:c>
+      <x:c r="D5" s="32" t="n">
+        <x:f>IF(C5="","",(1/'Metadata'!$B$5)^(C5-1))</x:f>
+        <x:v>430.4717298213029</x:v>
+      </x:c>
       <x:c r="E5" s="31" t="n">
-        <x:v>733.6327273358</x:v>
-      </x:c>
-      <x:c r="F5" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G5" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H5" s="32" t="n">
-        <x:f>IF(E5=0,"",I5/E5)</x:f>
-        <x:v>931.7239316710378</x:v>
-      </x:c>
-      <x:c r="I5" s="31" t="n">
-        <x:f>IF(C5=0,"",SUMIF('Species'!$H$2:$H$160,A5,'Species'!$U$2:$U$160))</x:f>
-        <x:v>683543.169115858</x:v>
-      </x:c>
-      <x:c r="J5" s="32" t="n">
-        <x:v>3.633944635497567</x:v>
-      </x:c>
-      <x:c r="K5" s="32" t="n">
-        <x:f>IF(J5="","",(1/'Metadata'!$B$5)^(J5-1))</x:f>
-        <x:v>430.4717298213029</x:v>
-      </x:c>
-      <x:c r="L5" s="31" t="n">
-        <x:f>IF(E5=0,"",E5*K5)</x:f>
+        <x:f>IF(B5=0,"",B5*D5)</x:f>
         <x:v>315808.14918976213</x:v>
-      </x:c>
-      <x:c r="M5" s="31" t="n">
-        <x:f>IF(E5=0,"",I5-L5)</x:f>
-        <x:v>367735.0199260959</x:v>
-      </x:c>
-      <x:c r="N5" s="32" t="n">
-        <x:f>IF(L5=0,"",I5/L5)</x:f>
-        <x:v>2.1644253666967033</x:v>
-      </x:c>
-      <x:c r="O5" s="34" t="n">
-        <x:f>IF(L5=0,"",M5/L5)</x:f>
-        <x:v>1.164425366696703</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="18" customHeight="1">
       <x:c r="A6" s="24" t="str">
         <x:v>Herring-likes</x:v>
       </x:c>
-      <x:c r="B6" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C6" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D6" s="31" t="n">
+      <x:c r="B6" s="31" t="n">
         <x:v>1608.1569821274</x:v>
       </x:c>
+      <x:c r="C6" s="32" t="n">
+        <x:v>3.0737956077031514</x:v>
+      </x:c>
+      <x:c r="D6" s="32" t="n">
+        <x:f>IF(C6="","",(1/'Metadata'!$B$5)^(C6-1))</x:f>
+        <x:v>118.5210820342795</x:v>
+      </x:c>
       <x:c r="E6" s="31" t="n">
-        <x:v>1608.1569821274</x:v>
-      </x:c>
-      <x:c r="F6" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G6" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H6" s="32" t="n">
-        <x:f>IF(E6=0,"",I6/E6)</x:f>
-        <x:v>121.75213089245219</x:v>
-      </x:c>
-      <x:c r="I6" s="31" t="n">
-        <x:f>IF(C6=0,"",SUMIF('Species'!$H$2:$H$160,A6,'Species'!$U$2:$U$160))</x:f>
-        <x:v>195796.5393835861</x:v>
-      </x:c>
-      <x:c r="J6" s="32" t="n">
-        <x:v>3.0737956077031514</x:v>
-      </x:c>
-      <x:c r="K6" s="32" t="n">
-        <x:f>IF(J6="","",(1/'Metadata'!$B$5)^(J6-1))</x:f>
-        <x:v>118.5210820342795</x:v>
-      </x:c>
-      <x:c r="L6" s="31" t="n">
-        <x:f>IF(E6=0,"",E6*K6)</x:f>
+        <x:f>IF(B6=0,"",B6*D6)</x:f>
         <x:v>190600.50560272092</x:v>
-      </x:c>
-      <x:c r="M6" s="31" t="n">
-        <x:f>IF(E6=0,"",I6-L6)</x:f>
-        <x:v>5196.0337808651675</x:v>
-      </x:c>
-      <x:c r="N6" s="32" t="n">
-        <x:f>IF(L6=0,"",I6/L6)</x:f>
-        <x:v>1.027261385086226</x:v>
-      </x:c>
-      <x:c r="O6" s="34" t="n">
-        <x:f>IF(L6=0,"",M6/L6)</x:f>
-        <x:v>0.027261385086226084</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="18" customHeight="1">
       <x:c r="A7" s="24" t="str">
         <x:v>Molluscs</x:v>
       </x:c>
-      <x:c r="B7" s="33" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="C7" s="33" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="D7" s="31" t="n">
+      <x:c r="B7" s="31" t="n">
         <x:v>1408.9252475538</x:v>
       </x:c>
+      <x:c r="C7" s="32" t="n">
+        <x:v>2.6858967695621563</x:v>
+      </x:c>
+      <x:c r="D7" s="32" t="n">
+        <x:f>IF(C7="","",(1/'Metadata'!$B$5)^(C7-1))</x:f>
+        <x:v>48.517316231415066</x:v>
+      </x:c>
       <x:c r="E7" s="31" t="n">
-        <x:v>1408.9252475538</x:v>
-      </x:c>
-      <x:c r="F7" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G7" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H7" s="32" t="n">
-        <x:f>IF(E7=0,"",I7/E7)</x:f>
-        <x:v>70.55690926758827</x:v>
-      </x:c>
-      <x:c r="I7" s="31" t="n">
-        <x:f>IF(C7=0,"",SUMIF('Species'!$H$2:$H$160,A7,'Species'!$U$2:$U$160))</x:f>
-        <x:v>99409.41085646782</x:v>
-      </x:c>
-      <x:c r="J7" s="32" t="n">
-        <x:v>2.6858967695621563</x:v>
-      </x:c>
-      <x:c r="K7" s="32" t="n">
-        <x:f>IF(J7="","",(1/'Metadata'!$B$5)^(J7-1))</x:f>
-        <x:v>48.517316231415066</x:v>
-      </x:c>
-      <x:c r="L7" s="31" t="n">
-        <x:f>IF(E7=0,"",E7*K7)</x:f>
+        <x:f>IF(B7=0,"",B7*D7)</x:f>
         <x:v>68357.27178199247</x:v>
-      </x:c>
-      <x:c r="M7" s="31" t="n">
-        <x:f>IF(E7=0,"",I7-L7)</x:f>
-        <x:v>31052.139074475344</x:v>
-      </x:c>
-      <x:c r="N7" s="32" t="n">
-        <x:f>IF(L7=0,"",I7/L7)</x:f>
-        <x:v>1.454262410786492</x:v>
-      </x:c>
-      <x:c r="O7" s="34" t="n">
-        <x:f>IF(L7=0,"",M7/L7)</x:f>
-        <x:v>0.45426241078649204</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="18" customHeight="1">
       <x:c r="A8" s="24" t="str">
         <x:v>Other fishes &amp; inverts</x:v>
       </x:c>
-      <x:c r="B8" s="33" t="n">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="C8" s="33" t="n">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="D8" s="31" t="n">
+      <x:c r="B8" s="31" t="n">
         <x:v>11418.245113671399</x:v>
       </x:c>
+      <x:c r="C8" s="32" t="n">
+        <x:v>3.709458512130325</x:v>
+      </x:c>
+      <x:c r="D8" s="32" t="n">
+        <x:f>IF(C8="","",(1/'Metadata'!$B$5)^(C8-1))</x:f>
+        <x:v>512.2223356603195</x:v>
+      </x:c>
       <x:c r="E8" s="31" t="n">
-        <x:v>11418.245113671399</x:v>
-      </x:c>
-      <x:c r="F8" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G8" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H8" s="32" t="n">
-        <x:f>IF(E8=0,"",I8/E8)</x:f>
-        <x:v>859.2394834655844</x:v>
-      </x:c>
-      <x:c r="I8" s="31" t="n">
-        <x:f>IF(C8=0,"",SUMIF('Species'!$H$2:$H$160,A8,'Species'!$U$2:$U$160))</x:f>
-        <x:v>9811007.033554446</x:v>
-      </x:c>
-      <x:c r="J8" s="32" t="n">
-        <x:v>3.709458512130325</x:v>
-      </x:c>
-      <x:c r="K8" s="32" t="n">
-        <x:f>IF(J8="","",(1/'Metadata'!$B$5)^(J8-1))</x:f>
-        <x:v>512.2223356603195</x:v>
-      </x:c>
-      <x:c r="L8" s="31" t="n">
-        <x:f>IF(E8=0,"",E8*K8)</x:f>
+        <x:f>IF(B8=0,"",B8*D8)</x:f>
         <x:v>5848680.181266794</x:v>
-      </x:c>
-      <x:c r="M8" s="31" t="n">
-        <x:f>IF(E8=0,"",I8-L8)</x:f>
-        <x:v>3962326.852287652</x:v>
-      </x:c>
-      <x:c r="N8" s="32" t="n">
-        <x:f>IF(L8=0,"",I8/L8)</x:f>
-        <x:v>1.6774736743135497</x:v>
-      </x:c>
-      <x:c r="O8" s="34" t="n">
-        <x:f>IF(L8=0,"",M8/L8)</x:f>
-        <x:v>0.6774736743135495</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="18" customHeight="1">
       <x:c r="A9" s="24" t="str">
         <x:v>Perch-likes</x:v>
       </x:c>
-      <x:c r="B9" s="33" t="n">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="C9" s="33" t="n">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="D9" s="31" t="n">
+      <x:c r="B9" s="31" t="n">
         <x:v>18161.308503594297</x:v>
       </x:c>
+      <x:c r="C9" s="32" t="n">
+        <x:v>3.5282095979427233</x:v>
+      </x:c>
+      <x:c r="D9" s="32" t="n">
+        <x:f>IF(C9="","",(1/'Metadata'!$B$5)^(C9-1))</x:f>
+        <x:v>337.4501285677891</x:v>
+      </x:c>
       <x:c r="E9" s="31" t="n">
-        <x:v>18161.308503594297</x:v>
-      </x:c>
-      <x:c r="F9" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G9" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H9" s="32" t="n">
-        <x:f>IF(E9=0,"",I9/E9)</x:f>
-        <x:v>536.6695656674364</x:v>
-      </x:c>
-      <x:c r="I9" s="31" t="n">
-        <x:f>IF(C9=0,"",SUMIF('Species'!$H$2:$H$160,A9,'Species'!$U$2:$U$160))</x:f>
-        <x:v>9746621.546576269</x:v>
-      </x:c>
-      <x:c r="J9" s="32" t="n">
-        <x:v>3.5282095979427233</x:v>
-      </x:c>
-      <x:c r="K9" s="32" t="n">
-        <x:f>IF(J9="","",(1/'Metadata'!$B$5)^(J9-1))</x:f>
-        <x:v>337.4501285677891</x:v>
-      </x:c>
-      <x:c r="L9" s="31" t="n">
-        <x:f>IF(E9=0,"",E9*K9)</x:f>
+        <x:f>IF(B9=0,"",B9*D9)</x:f>
         <x:v>6128535.889497177</x:v>
-      </x:c>
-      <x:c r="M9" s="31" t="n">
-        <x:f>IF(E9=0,"",I9-L9)</x:f>
-        <x:v>3618085.657079092</x:v>
-      </x:c>
-      <x:c r="N9" s="32" t="n">
-        <x:f>IF(L9=0,"",I9/L9)</x:f>
-        <x:v>1.590367050518479</x:v>
-      </x:c>
-      <x:c r="O9" s="34" t="n">
-        <x:f>IF(L9=0,"",M9/L9)</x:f>
-        <x:v>0.5903670505184792</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="18" customHeight="1">
       <x:c r="A10" s="24" t="str">
         <x:v>Salmon, smelts, etc</x:v>
       </x:c>
-      <x:c r="B10" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C10" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D10" s="31" t="n">
+      <x:c r="B10" s="31" t="n">
         <x:v>9.165646156900001</x:v>
       </x:c>
+      <x:c r="C10" s="32" t="n">
+        <x:v>3.35</x:v>
+      </x:c>
+      <x:c r="D10" s="32" t="n">
+        <x:f>IF(C10="","",(1/'Metadata'!$B$5)^(C10-1))</x:f>
+        <x:v>223.872113856834</x:v>
+      </x:c>
       <x:c r="E10" s="31" t="n">
-        <x:v>9.165646156900001</x:v>
-      </x:c>
-      <x:c r="F10" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G10" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H10" s="32" t="n">
-        <x:f>IF(E10=0,"",I10/E10)</x:f>
-        <x:v>223.872113856834</x:v>
-      </x:c>
-      <x:c r="I10" s="31" t="n">
-        <x:f>IF(C10=0,"",SUMIF('Species'!$H$2:$H$160,A10,'Species'!$U$2:$U$160))</x:f>
+        <x:f>IF(B10=0,"",B10*D10)</x:f>
         <x:v>2051.93258000897</x:v>
-      </x:c>
-      <x:c r="J10" s="32" t="n">
-        <x:v>3.35</x:v>
-      </x:c>
-      <x:c r="K10" s="32" t="n">
-        <x:f>IF(J10="","",(1/'Metadata'!$B$5)^(J10-1))</x:f>
-        <x:v>223.872113856834</x:v>
-      </x:c>
-      <x:c r="L10" s="31" t="n">
-        <x:f>IF(E10=0,"",E10*K10)</x:f>
-        <x:v>2051.93258000897</x:v>
-      </x:c>
-      <x:c r="M10" s="31" t="n">
-        <x:f>IF(E10=0,"",I10-L10)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N10" s="32" t="n">
-        <x:f>IF(L10=0,"",I10/L10)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O10" s="34" t="n">
-        <x:f>IF(L10=0,"",M10/L10)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="18" customHeight="1">
       <x:c r="A11" s="24" t="str">
         <x:v>Scorpionfishes</x:v>
       </x:c>
-      <x:c r="B11" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C11" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D11" s="31" t="n">
+      <x:c r="B11" s="31" t="n">
         <x:v>1936.5553467619</x:v>
       </x:c>
+      <x:c r="C11" s="32" t="n">
+        <x:v>3.8219587193253175</x:v>
+      </x:c>
+      <x:c r="D11" s="32" t="n">
+        <x:f>IF(C11="","",(1/'Metadata'!$B$5)^(C11-1))</x:f>
+        <x:v>663.6799831172661</x:v>
+      </x:c>
       <x:c r="E11" s="31" t="n">
-        <x:v>1936.5553467619</x:v>
-      </x:c>
-      <x:c r="F11" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G11" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H11" s="32" t="n">
-        <x:f>IF(E11=0,"",I11/E11)</x:f>
-        <x:v>672.2337849502396</x:v>
-      </x:c>
-      <x:c r="I11" s="31" t="n">
-        <x:f>IF(C11=0,"",SUMIF('Species'!$H$2:$H$160,A11,'Species'!$U$2:$U$160))</x:f>
-        <x:v>1301817.9305193757</x:v>
-      </x:c>
-      <x:c r="J11" s="32" t="n">
-        <x:v>3.8219587193253175</x:v>
-      </x:c>
-      <x:c r="K11" s="32" t="n">
-        <x:f>IF(J11="","",(1/'Metadata'!$B$5)^(J11-1))</x:f>
-        <x:v>663.6799831172661</x:v>
-      </x:c>
-      <x:c r="L11" s="31" t="n">
-        <x:f>IF(E11=0,"",E11*K11)</x:f>
+        <x:f>IF(B11=0,"",B11*D11)</x:f>
         <x:v>1285253.0198445893</x:v>
-      </x:c>
-      <x:c r="M11" s="31" t="n">
-        <x:f>IF(E11=0,"",I11-L11)</x:f>
-        <x:v>16564.910674786428</x:v>
-      </x:c>
-      <x:c r="N11" s="32" t="n">
-        <x:f>IF(L11=0,"",I11/L11)</x:f>
-        <x:v>1.0128884433018406</x:v>
-      </x:c>
-      <x:c r="O11" s="34" t="n">
-        <x:f>IF(L11=0,"",M11/L11)</x:f>
-        <x:v>0.012888443301840621</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="18" customHeight="1">
       <x:c r="A12" s="24" t="str">
         <x:v>Sharks &amp; rays</x:v>
       </x:c>
-      <x:c r="B12" s="33" t="n">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="C12" s="33" t="n">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="D12" s="31" t="n">
+      <x:c r="B12" s="31" t="n">
         <x:v>1941.9561008534</x:v>
       </x:c>
+      <x:c r="C12" s="32" t="n">
+        <x:v>4.013336835948673</x:v>
+      </x:c>
+      <x:c r="D12" s="32" t="n">
+        <x:f>IF(C12="","",(1/'Metadata'!$B$5)^(C12-1))</x:f>
+        <x:v>1031.1855911433568</x:v>
+      </x:c>
       <x:c r="E12" s="31" t="n">
-        <x:v>1941.9561008534</x:v>
-      </x:c>
-      <x:c r="F12" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G12" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H12" s="32" t="n">
-        <x:f>IF(E12=0,"",I12/E12)</x:f>
-        <x:v>1208.0215854397632</x:v>
-      </x:c>
-      <x:c r="I12" s="31" t="n">
-        <x:f>IF(C12=0,"",SUMIF('Species'!$H$2:$H$160,A12,'Species'!$U$2:$U$160))</x:f>
-        <x:v>2345924.8878073446</x:v>
-      </x:c>
-      <x:c r="J12" s="32" t="n">
-        <x:v>4.013336835948673</x:v>
-      </x:c>
-      <x:c r="K12" s="32" t="n">
-        <x:f>IF(J12="","",(1/'Metadata'!$B$5)^(J12-1))</x:f>
-        <x:v>1031.1855911433568</x:v>
-      </x:c>
-      <x:c r="L12" s="31" t="n">
-        <x:f>IF(E12=0,"",E12*K12)</x:f>
+        <x:f>IF(B12=0,"",B12*D12)</x:f>
         <x:v>2002517.1498329614</x:v>
-      </x:c>
-      <x:c r="M12" s="31" t="n">
-        <x:f>IF(E12=0,"",I12-L12)</x:f>
-        <x:v>343407.73797438317</x:v>
-      </x:c>
-      <x:c r="N12" s="32" t="n">
-        <x:f>IF(L12=0,"",I12/L12)</x:f>
-        <x:v>1.17148803844353</x:v>
-      </x:c>
-      <x:c r="O12" s="34" t="n">
-        <x:f>IF(L12=0,"",M12/L12)</x:f>
-        <x:v>0.17148803844353008</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="18" customHeight="1">
       <x:c r="A13" s="24" t="str">
         <x:v>Tuna &amp; billfishes</x:v>
       </x:c>
-      <x:c r="B13" s="33" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="C13" s="33" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="D13" s="31" t="n">
+      <x:c r="B13" s="31" t="n">
         <x:v>420.37662623460005</x:v>
       </x:c>
+      <x:c r="C13" s="32" t="n">
+        <x:v>4.4488024282497785</x:v>
+      </x:c>
+      <x:c r="D13" s="32" t="n">
+        <x:f>IF(C13="","",(1/'Metadata'!$B$5)^(C13-1))</x:f>
+        <x:v>2810.6219151851446</x:v>
+      </x:c>
       <x:c r="E13" s="31" t="n">
-        <x:v>420.37662623460005</x:v>
-      </x:c>
-      <x:c r="F13" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G13" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H13" s="32" t="n">
-        <x:f>IF(E13=0,"",I13/E13)</x:f>
-        <x:v>2818.6825740980757</x:v>
-      </x:c>
-      <x:c r="I13" s="31" t="n">
-        <x:f>IF(C13=0,"",SUMIF('Species'!$H$2:$H$160,A13,'Species'!$U$2:$U$160))</x:f>
-        <x:v>1184908.270925607</x:v>
-      </x:c>
-      <x:c r="J13" s="32" t="n">
-        <x:v>4.4488024282497785</x:v>
-      </x:c>
-      <x:c r="K13" s="32" t="n">
-        <x:f>IF(J13="","",(1/'Metadata'!$B$5)^(J13-1))</x:f>
-        <x:v>2810.6219151851446</x:v>
-      </x:c>
-      <x:c r="L13" s="31" t="n">
-        <x:f>IF(E13=0,"",E13*K13)</x:f>
+        <x:f>IF(B13=0,"",B13*D13)</x:f>
         <x:v>1181519.7583265614</x:v>
       </x:c>
-      <x:c r="M13" s="31" t="n">
-        <x:f>IF(E13=0,"",I13-L13)</x:f>
-        <x:v>3388.5125990456436</x:v>
-      </x:c>
-      <x:c r="N13" s="32" t="n">
-        <x:f>IF(L13=0,"",I13/L13)</x:f>
-        <x:v>1.002867927154976</x:v>
-      </x:c>
-      <x:c r="O13" s="34" t="n">
-        <x:f>IF(L13=0,"",M13/L13)</x:f>
-        <x:v>0.002867927154976184</x:v>
-      </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="G2:G13">
-    <x:cfRule type="cellIs" dxfId="1" priority="1" operator="lessThan">
-      <x:formula>0.9</x:formula>
-    </x:cfRule>
-  </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="O2:O13">
-    <x:cfRule type="dataBar" priority="2">
-      <x:dataBar>
-        <x:cfvo type="min"/>
-        <x:cfvo type="max"/>
-        <x:color rgb="FFE28A32"/>
-      </x:dataBar>
-    </x:cfRule>
-  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbe4d89f7b6bc4823"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7b076894aa8d4879"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -12095,20 +11575,10 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="34" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="15" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="15" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="16" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
@@ -12116,1416 +11586,497 @@
         <x:v>functional_group</x:v>
       </x:c>
       <x:c r="B1" s="29" t="str">
-        <x:v>taxon_count_total</x:v>
+        <x:v>catch_tonnes_matched</x:v>
       </x:c>
       <x:c r="C1" s="29" t="str">
-        <x:v>taxon_count_matched</x:v>
+        <x:v>tl_weighted</x:v>
       </x:c>
       <x:c r="D1" s="29" t="str">
-        <x:v>catch_tonnes_total</x:v>
+        <x:v>sppr</x:v>
       </x:c>
       <x:c r="E1" s="29" t="str">
-        <x:v>catch_tonnes_matched</x:v>
-      </x:c>
-      <x:c r="F1" s="29" t="str">
-        <x:v>catch_tonnes_missing_tl</x:v>
-      </x:c>
-      <x:c r="G1" s="29" t="str">
-        <x:v>catch_coverage_fraction</x:v>
-      </x:c>
-      <x:c r="H1" s="29" t="str">
-        <x:v>sppr_correct</x:v>
-      </x:c>
-      <x:c r="I1" s="29" t="str">
-        <x:v>ppr_correct</x:v>
-      </x:c>
-      <x:c r="J1" s="29" t="str">
-        <x:v>tl_weighted_jensen</x:v>
-      </x:c>
-      <x:c r="K1" s="29" t="str">
-        <x:v>sppr_jensen</x:v>
-      </x:c>
-      <x:c r="L1" s="29" t="str">
-        <x:v>ppr_jensen</x:v>
-      </x:c>
-      <x:c r="M1" s="29" t="str">
-        <x:v>jensen_difference</x:v>
-      </x:c>
-      <x:c r="N1" s="29" t="str">
-        <x:v>jensen_ratio_correct_to_error</x:v>
-      </x:c>
-      <x:c r="O1" s="29" t="str">
-        <x:v>jensen_percent_difference</x:v>
+        <x:v>ppr</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="18" customHeight="1">
       <x:c r="A2" s="24" t="str">
         <x:v>Cephalopods</x:v>
       </x:c>
-      <x:c r="B2" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="C2" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="D2" s="31" t="n">
+      <x:c r="B2" s="31" t="n">
         <x:v>6281.261316057501</x:v>
       </x:c>
+      <x:c r="C2" s="32" t="n">
+        <x:v>3.73691931112171</x:v>
+      </x:c>
+      <x:c r="D2" s="32" t="n">
+        <x:f>IF(C2="","",(1/'Metadata'!$B$5)^(C2-1))</x:f>
+        <x:v>545.65647251538</x:v>
+      </x:c>
       <x:c r="E2" s="31" t="n">
-        <x:v>6281.261316057501</x:v>
-      </x:c>
-      <x:c r="F2" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G2" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H2" s="32" t="n">
-        <x:f>IF(E2=0,"",I2/E2)</x:f>
-        <x:v>646.6243934280495</x:v>
-      </x:c>
-      <x:c r="I2" s="31" t="n">
-        <x:f>IF(C2=0,"",SUMIF('Species'!$G$2:$G$160,A2,'Species'!$U$2:$U$160))</x:f>
-        <x:v>4061616.7884587534</x:v>
-      </x:c>
-      <x:c r="J2" s="32" t="n">
-        <x:v>3.73691931112171</x:v>
-      </x:c>
-      <x:c r="K2" s="32" t="n">
-        <x:f>IF(J2="","",(1/'Metadata'!$B$5)^(J2-1))</x:f>
-        <x:v>545.65647251538</x:v>
-      </x:c>
-      <x:c r="L2" s="31" t="n">
-        <x:f>IF(E2=0,"",E2*K2)</x:f>
+        <x:f>IF(B2=0,"",B2*D2)</x:f>
         <x:v>3427410.8926672493</x:v>
-      </x:c>
-      <x:c r="M2" s="31" t="n">
-        <x:f>IF(E2=0,"",I2-L2)</x:f>
-        <x:v>634205.8957915041</x:v>
-      </x:c>
-      <x:c r="N2" s="32" t="n">
-        <x:f>IF(L2=0,"",I2/L2)</x:f>
-        <x:v>1.1850393535097736</x:v>
-      </x:c>
-      <x:c r="O2" s="34" t="n">
-        <x:f>IF(L2=0,"",M2/L2)</x:f>
-        <x:v>0.18503935350977366</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="18" customHeight="1">
       <x:c r="A3" s="24" t="str">
         <x:v>Large bathydemersals (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B3" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C3" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D3" s="31" t="n">
+      <x:c r="B3" s="31" t="n">
         <x:v>6.8752753339</x:v>
       </x:c>
+      <x:c r="C3" s="32" t="n">
+        <x:v>3.82</x:v>
+      </x:c>
+      <x:c r="D3" s="32" t="n">
+        <x:f>IF(C3="","",(1/'Metadata'!$B$5)^(C3-1))</x:f>
+        <x:v>660.6934480075957</x:v>
+      </x:c>
       <x:c r="E3" s="31" t="n">
-        <x:v>6.8752753339</x:v>
-      </x:c>
-      <x:c r="F3" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G3" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H3" s="32" t="n">
-        <x:f>IF(E3=0,"",I3/E3)</x:f>
-        <x:v>660.6934480075957</x:v>
-      </x:c>
-      <x:c r="I3" s="31" t="n">
-        <x:f>IF(C3=0,"",SUMIF('Species'!$G$2:$G$160,A3,'Species'!$U$2:$U$160))</x:f>
+        <x:f>IF(B3=0,"",B3*D3)</x:f>
         <x:v>4542.449366355965</x:v>
-      </x:c>
-      <x:c r="J3" s="32" t="n">
-        <x:v>3.82</x:v>
-      </x:c>
-      <x:c r="K3" s="32" t="n">
-        <x:f>IF(J3="","",(1/'Metadata'!$B$5)^(J3-1))</x:f>
-        <x:v>660.6934480075957</x:v>
-      </x:c>
-      <x:c r="L3" s="31" t="n">
-        <x:f>IF(E3=0,"",E3*K3)</x:f>
-        <x:v>4542.449366355965</x:v>
-      </x:c>
-      <x:c r="M3" s="31" t="n">
-        <x:f>IF(E3=0,"",I3-L3)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N3" s="32" t="n">
-        <x:f>IF(L3=0,"",I3/L3)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O3" s="34" t="n">
-        <x:f>IF(L3=0,"",M3/L3)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="18" customHeight="1">
       <x:c r="A4" s="24" t="str">
         <x:v>Large benthopelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B4" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C4" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D4" s="31" t="n">
+      <x:c r="B4" s="31" t="n">
         <x:v>180.8074056741</x:v>
       </x:c>
+      <x:c r="C4" s="32" t="n">
+        <x:v>2.6589630686173336</x:v>
+      </x:c>
+      <x:c r="D4" s="32" t="n">
+        <x:f>IF(C4="","",(1/'Metadata'!$B$5)^(C4-1))</x:f>
+        <x:v>45.599813729195354</x:v>
+      </x:c>
       <x:c r="E4" s="31" t="n">
-        <x:v>180.8074056741</x:v>
-      </x:c>
-      <x:c r="F4" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G4" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H4" s="32" t="n">
-        <x:f>IF(E4=0,"",I4/E4)</x:f>
-        <x:v>384.8633404025366</x:v>
-      </x:c>
-      <x:c r="I4" s="31" t="n">
-        <x:f>IF(C4=0,"",SUMIF('Species'!$G$2:$G$160,A4,'Species'!$U$2:$U$160))</x:f>
-        <x:v>69586.14211725068</x:v>
-      </x:c>
-      <x:c r="J4" s="32" t="n">
-        <x:v>2.6589630686173336</x:v>
-      </x:c>
-      <x:c r="K4" s="32" t="n">
-        <x:f>IF(J4="","",(1/'Metadata'!$B$5)^(J4-1))</x:f>
-        <x:v>45.599813729195354</x:v>
-      </x:c>
-      <x:c r="L4" s="31" t="n">
-        <x:f>IF(E4=0,"",E4*K4)</x:f>
+        <x:f>IF(B4=0,"",B4*D4)</x:f>
         <x:v>8244.784019598019</x:v>
-      </x:c>
-      <x:c r="M4" s="31" t="n">
-        <x:f>IF(E4=0,"",I4-L4)</x:f>
-        <x:v>61341.358097652665</x:v>
-      </x:c>
-      <x:c r="N4" s="32" t="n">
-        <x:f>IF(L4=0,"",I4/L4)</x:f>
-        <x:v>8.440020011663497</x:v>
-      </x:c>
-      <x:c r="O4" s="34" t="n">
-        <x:f>IF(L4=0,"",M4/L4)</x:f>
-        <x:v>7.4400200116634965</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="18" customHeight="1">
       <x:c r="A5" s="24" t="str">
         <x:v>Large demersals (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B5" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C5" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D5" s="31" t="n">
+      <x:c r="B5" s="31" t="n">
         <x:v>5110.1888105527005</x:v>
       </x:c>
+      <x:c r="C5" s="32" t="n">
+        <x:v>4.2529020842281575</x:v>
+      </x:c>
+      <x:c r="D5" s="32" t="n">
+        <x:f>IF(C5="","",(1/'Metadata'!$B$5)^(C5-1))</x:f>
+        <x:v>1790.2021906264351</x:v>
+      </x:c>
       <x:c r="E5" s="31" t="n">
-        <x:v>5110.1888105527005</x:v>
-      </x:c>
-      <x:c r="F5" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G5" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H5" s="32" t="n">
-        <x:f>IF(E5=0,"",I5/E5)</x:f>
-        <x:v>2146.3189494951735</x:v>
-      </x:c>
-      <x:c r="I5" s="31" t="n">
-        <x:f>IF(C5=0,"",SUMIF('Species'!$G$2:$G$160,A5,'Species'!$U$2:$U$160))</x:f>
-        <x:v>10968095.079587461</x:v>
-      </x:c>
-      <x:c r="J5" s="32" t="n">
-        <x:v>4.2529020842281575</x:v>
-      </x:c>
-      <x:c r="K5" s="32" t="n">
-        <x:f>IF(J5="","",(1/'Metadata'!$B$5)^(J5-1))</x:f>
-        <x:v>1790.2021906264351</x:v>
-      </x:c>
-      <x:c r="L5" s="31" t="n">
-        <x:f>IF(E5=0,"",E5*K5)</x:f>
+        <x:f>IF(B5=0,"",B5*D5)</x:f>
         <x:v>9148271.203166142</x:v>
-      </x:c>
-      <x:c r="M5" s="31" t="n">
-        <x:f>IF(E5=0,"",I5-L5)</x:f>
-        <x:v>1819823.8764213193</x:v>
-      </x:c>
-      <x:c r="N5" s="32" t="n">
-        <x:f>IF(L5=0,"",I5/L5)</x:f>
-        <x:v>1.198925440228695</x:v>
-      </x:c>
-      <x:c r="O5" s="34" t="n">
-        <x:f>IF(L5=0,"",M5/L5)</x:f>
-        <x:v>0.19892544022869513</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="18" customHeight="1">
       <x:c r="A6" s="24" t="str">
         <x:v>Large flatfishes (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B6" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C6" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D6" s="31" t="n">
+      <x:c r="B6" s="31" t="n">
         <x:v>46.2828961022</x:v>
       </x:c>
+      <x:c r="C6" s="32" t="n">
+        <x:v>4.36</x:v>
+      </x:c>
+      <x:c r="D6" s="32" t="n">
+        <x:f>IF(C6="","",(1/'Metadata'!$B$5)^(C6-1))</x:f>
+        <x:v>2290.867652767775</x:v>
+      </x:c>
       <x:c r="E6" s="31" t="n">
-        <x:v>46.2828961022</x:v>
-      </x:c>
-      <x:c r="F6" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G6" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H6" s="32" t="n">
-        <x:f>IF(E6=0,"",I6/E6)</x:f>
-        <x:v>2290.867652767775</x:v>
-      </x:c>
-      <x:c r="I6" s="31" t="n">
-        <x:f>IF(C6=0,"",SUMIF('Species'!$G$2:$G$160,A6,'Species'!$U$2:$U$160))</x:f>
+        <x:f>IF(B6=0,"",B6*D6)</x:f>
         <x:v>106027.98955694171</x:v>
-      </x:c>
-      <x:c r="J6" s="32" t="n">
-        <x:v>4.36</x:v>
-      </x:c>
-      <x:c r="K6" s="32" t="n">
-        <x:f>IF(J6="","",(1/'Metadata'!$B$5)^(J6-1))</x:f>
-        <x:v>2290.867652767775</x:v>
-      </x:c>
-      <x:c r="L6" s="31" t="n">
-        <x:f>IF(E6=0,"",E6*K6)</x:f>
-        <x:v>106027.98955694171</x:v>
-      </x:c>
-      <x:c r="M6" s="31" t="n">
-        <x:f>IF(E6=0,"",I6-L6)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N6" s="32" t="n">
-        <x:f>IF(L6=0,"",I6/L6)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O6" s="34" t="n">
-        <x:f>IF(L6=0,"",M6/L6)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="18" customHeight="1">
       <x:c r="A7" s="24" t="str">
         <x:v>Large pelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B7" s="33" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="C7" s="33" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="D7" s="31" t="n">
+      <x:c r="B7" s="31" t="n">
         <x:v>414.9087926017</x:v>
       </x:c>
+      <x:c r="C7" s="32" t="n">
+        <x:v>4.44988020276366</x:v>
+      </x:c>
+      <x:c r="D7" s="32" t="n">
+        <x:f>IF(C7="","",(1/'Metadata'!$B$5)^(C7-1))</x:f>
+        <x:v>2817.605606344727</x:v>
+      </x:c>
       <x:c r="E7" s="31" t="n">
-        <x:v>414.9087926017</x:v>
-      </x:c>
-      <x:c r="F7" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G7" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H7" s="32" t="n">
-        <x:f>IF(E7=0,"",I7/E7)</x:f>
-        <x:v>2821.239402876913</x:v>
-      </x:c>
-      <x:c r="I7" s="31" t="n">
-        <x:f>IF(C7=0,"",SUMIF('Species'!$G$2:$G$160,A7,'Species'!$U$2:$U$160))</x:f>
-        <x:v>1170557.034288001</x:v>
-      </x:c>
-      <x:c r="J7" s="32" t="n">
-        <x:v>4.44988020276366</x:v>
-      </x:c>
-      <x:c r="K7" s="32" t="n">
-        <x:f>IF(J7="","",(1/'Metadata'!$B$5)^(J7-1))</x:f>
-        <x:v>2817.605606344727</x:v>
-      </x:c>
-      <x:c r="L7" s="31" t="n">
-        <x:f>IF(E7=0,"",E7*K7)</x:f>
+        <x:f>IF(B7=0,"",B7*D7)</x:f>
         <x:v>1169049.3401562716</x:v>
-      </x:c>
-      <x:c r="M7" s="31" t="n">
-        <x:f>IF(E7=0,"",I7-L7)</x:f>
-        <x:v>1507.6941317294259</x:v>
-      </x:c>
-      <x:c r="N7" s="32" t="n">
-        <x:f>IF(L7=0,"",I7/L7)</x:f>
-        <x:v>1.0012896753626566</x:v>
-      </x:c>
-      <x:c r="O7" s="34" t="n">
-        <x:f>IF(L7=0,"",M7/L7)</x:f>
-        <x:v>0.001289675362656538</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="18" customHeight="1">
       <x:c r="A8" s="24" t="str">
         <x:v>Large rays (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B8" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="C8" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="D8" s="31" t="n">
+      <x:c r="B8" s="31" t="n">
         <x:v>456.7059529942</x:v>
       </x:c>
+      <x:c r="C8" s="32" t="n">
+        <x:v>3.816100029825476</x:v>
+      </x:c>
+      <x:c r="D8" s="32" t="n">
+        <x:f>IF(C8="","",(1/'Metadata'!$B$5)^(C8-1))</x:f>
+        <x:v>654.7869719402023</x:v>
+      </x:c>
       <x:c r="E8" s="31" t="n">
-        <x:v>456.7059529942</x:v>
-      </x:c>
-      <x:c r="F8" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G8" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H8" s="32" t="n">
-        <x:f>IF(E8=0,"",I8/E8)</x:f>
-        <x:v>679.221082340696</x:v>
-      </x:c>
-      <x:c r="I8" s="31" t="n">
-        <x:f>IF(C8=0,"",SUMIF('Species'!$G$2:$G$160,A8,'Species'!$U$2:$U$160))</x:f>
-        <x:v>310204.31170415954</x:v>
-      </x:c>
-      <x:c r="J8" s="32" t="n">
-        <x:v>3.816100029825476</x:v>
-      </x:c>
-      <x:c r="K8" s="32" t="n">
-        <x:f>IF(J8="","",(1/'Metadata'!$B$5)^(J8-1))</x:f>
-        <x:v>654.7869719402023</x:v>
-      </x:c>
-      <x:c r="L8" s="31" t="n">
-        <x:f>IF(E8=0,"",E8*K8)</x:f>
+        <x:f>IF(B8=0,"",B8*D8)</x:f>
         <x:v>299045.1080281366</x:v>
-      </x:c>
-      <x:c r="M8" s="31" t="n">
-        <x:f>IF(E8=0,"",I8-L8)</x:f>
-        <x:v>11159.203676022938</x:v>
-      </x:c>
-      <x:c r="N8" s="32" t="n">
-        <x:f>IF(L8=0,"",I8/L8)</x:f>
-        <x:v>1.0373161218038485</x:v>
-      </x:c>
-      <x:c r="O8" s="34" t="n">
-        <x:f>IF(L8=0,"",M8/L8)</x:f>
-        <x:v>0.037316121803848364</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="18" customHeight="1">
       <x:c r="A9" s="24" t="str">
         <x:v>Large reef assoc. fish (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B9" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C9" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D9" s="31" t="n">
+      <x:c r="B9" s="31" t="n">
         <x:v>483.547522576</x:v>
       </x:c>
+      <x:c r="C9" s="32" t="n">
+        <x:v>3.9336675219692623</x:v>
+      </x:c>
+      <x:c r="D9" s="32" t="n">
+        <x:f>IF(C9="","",(1/'Metadata'!$B$5)^(C9-1))</x:f>
+        <x:v>858.3561476708641</x:v>
+      </x:c>
       <x:c r="E9" s="31" t="n">
-        <x:v>483.547522576</x:v>
-      </x:c>
-      <x:c r="F9" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G9" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H9" s="32" t="n">
-        <x:f>IF(E9=0,"",I9/E9)</x:f>
-        <x:v>881.4220381398429</x:v>
-      </x:c>
-      <x:c r="I9" s="31" t="n">
-        <x:f>IF(C9=0,"",SUMIF('Species'!$G$2:$G$160,A9,'Species'!$U$2:$U$160))</x:f>
-        <x:v>426209.44288640964</x:v>
-      </x:c>
-      <x:c r="J9" s="32" t="n">
-        <x:v>3.9336675219692623</x:v>
-      </x:c>
-      <x:c r="K9" s="32" t="n">
-        <x:f>IF(J9="","",(1/'Metadata'!$B$5)^(J9-1))</x:f>
-        <x:v>858.3561476708641</x:v>
-      </x:c>
-      <x:c r="L9" s="31" t="n">
-        <x:f>IF(E9=0,"",E9*K9)</x:f>
+        <x:f>IF(B9=0,"",B9*D9)</x:f>
         <x:v>415055.98869412555</x:v>
-      </x:c>
-      <x:c r="M9" s="31" t="n">
-        <x:f>IF(E9=0,"",I9-L9)</x:f>
-        <x:v>11153.454192284087</x:v>
-      </x:c>
-      <x:c r="N9" s="32" t="n">
-        <x:f>IF(L9=0,"",I9/L9)</x:f>
-        <x:v>1.0268721678426465</x:v>
-      </x:c>
-      <x:c r="O9" s="34" t="n">
-        <x:f>IF(L9=0,"",M9/L9)</x:f>
-        <x:v>0.026872167842646396</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="18" customHeight="1">
       <x:c r="A10" s="24" t="str">
         <x:v>Large sharks (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B10" s="33" t="n">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C10" s="33" t="n">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="D10" s="31" t="n">
+      <x:c r="B10" s="31" t="n">
         <x:v>1174.7488760033002</x:v>
       </x:c>
+      <x:c r="C10" s="32" t="n">
+        <x:v>4.134059408639334</x:v>
+      </x:c>
+      <x:c r="D10" s="32" t="n">
+        <x:f>IF(C10="","",(1/'Metadata'!$B$5)^(C10-1))</x:f>
+        <x:v>1361.6309319159682</x:v>
+      </x:c>
       <x:c r="E10" s="31" t="n">
-        <x:v>1174.7488760033002</x:v>
-      </x:c>
-      <x:c r="F10" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G10" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H10" s="32" t="n">
-        <x:f>IF(E10=0,"",I10/E10)</x:f>
-        <x:v>1530.3622899887575</x:v>
-      </x:c>
-      <x:c r="I10" s="31" t="n">
-        <x:f>IF(C10=0,"",SUMIF('Species'!$G$2:$G$160,A10,'Species'!$U$2:$U$160))</x:f>
-        <x:v>1797791.3800421294</x:v>
-      </x:c>
-      <x:c r="J10" s="32" t="n">
-        <x:v>4.134059408639334</x:v>
-      </x:c>
-      <x:c r="K10" s="32" t="n">
-        <x:f>IF(J10="","",(1/'Metadata'!$B$5)^(J10-1))</x:f>
-        <x:v>1361.6309319159682</x:v>
-      </x:c>
-      <x:c r="L10" s="31" t="n">
-        <x:f>IF(E10=0,"",E10*K10)</x:f>
+        <x:f>IF(B10=0,"",B10*D10)</x:f>
         <x:v>1599574.4067996098</x:v>
-      </x:c>
-      <x:c r="M10" s="31" t="n">
-        <x:f>IF(E10=0,"",I10-L10)</x:f>
-        <x:v>198216.97324251966</x:v>
-      </x:c>
-      <x:c r="N10" s="32" t="n">
-        <x:f>IF(L10=0,"",I10/L10)</x:f>
-        <x:v>1.1239185700895948</x:v>
-      </x:c>
-      <x:c r="O10" s="34" t="n">
-        <x:f>IF(L10=0,"",M10/L10)</x:f>
-        <x:v>0.12391857008959492</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="18" customHeight="1">
       <x:c r="A11" s="24" t="str">
         <x:v>Lobsters, crabs</x:v>
       </x:c>
-      <x:c r="B11" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="C11" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="D11" s="31" t="n">
+      <x:c r="B11" s="31" t="n">
         <x:v>116.75698116250003</x:v>
       </x:c>
+      <x:c r="C11" s="32" t="n">
+        <x:v>3.3211862134825254</x:v>
+      </x:c>
+      <x:c r="D11" s="32" t="n">
+        <x:f>IF(C11="","",(1/'Metadata'!$B$5)^(C11-1))</x:f>
+        <x:v>209.50105459757404</x:v>
+      </x:c>
       <x:c r="E11" s="31" t="n">
-        <x:v>116.75698116250003</x:v>
-      </x:c>
-      <x:c r="F11" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G11" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H11" s="32" t="n">
-        <x:f>IF(E11=0,"",I11/E11)</x:f>
-        <x:v>230.8791994091426</x:v>
-      </x:c>
-      <x:c r="I11" s="31" t="n">
-        <x:f>IF(C11=0,"",SUMIF('Species'!$G$2:$G$160,A11,'Species'!$U$2:$U$160))</x:f>
-        <x:v>26956.758336226347</x:v>
-      </x:c>
-      <x:c r="J11" s="32" t="n">
-        <x:v>3.3211862134825254</x:v>
-      </x:c>
-      <x:c r="K11" s="32" t="n">
-        <x:f>IF(J11="","",(1/'Metadata'!$B$5)^(J11-1))</x:f>
-        <x:v>209.50105459757404</x:v>
-      </x:c>
-      <x:c r="L11" s="31" t="n">
-        <x:f>IF(E11=0,"",E11*K11)</x:f>
+        <x:f>IF(B11=0,"",B11*D11)</x:f>
         <x:v>24460.710685172842</x:v>
-      </x:c>
-      <x:c r="M11" s="31" t="n">
-        <x:f>IF(E11=0,"",I11-L11)</x:f>
-        <x:v>2496.0476510535045</x:v>
-      </x:c>
-      <x:c r="N11" s="32" t="n">
-        <x:f>IF(L11=0,"",I11/L11)</x:f>
-        <x:v>1.1020431369791113</x:v>
-      </x:c>
-      <x:c r="O11" s="34" t="n">
-        <x:f>IF(L11=0,"",M11/L11)</x:f>
-        <x:v>0.10204313697911133</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="18" customHeight="1">
       <x:c r="A12" s="24" t="str">
         <x:v>Medium bathydemersals (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B12" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C12" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D12" s="31" t="n">
+      <x:c r="B12" s="31" t="n">
         <x:v>1515.656974349</x:v>
       </x:c>
+      <x:c r="C12" s="32" t="n">
+        <x:v>4.453287486940421</x:v>
+      </x:c>
+      <x:c r="D12" s="32" t="n">
+        <x:f>IF(C12="","",(1/'Metadata'!$B$5)^(C12-1))</x:f>
+        <x:v>2839.798248160936</x:v>
+      </x:c>
       <x:c r="E12" s="31" t="n">
-        <x:v>1515.656974349</x:v>
-      </x:c>
-      <x:c r="F12" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G12" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H12" s="32" t="n">
-        <x:f>IF(E12=0,"",I12/E12)</x:f>
-        <x:v>2867.9446971436923</x:v>
-      </x:c>
-      <x:c r="I12" s="31" t="n">
-        <x:f>IF(C12=0,"",SUMIF('Species'!$G$2:$G$160,A12,'Species'!$U$2:$U$160))</x:f>
-        <x:v>4346820.382273068</x:v>
-      </x:c>
-      <x:c r="J12" s="32" t="n">
-        <x:v>4.453287486940421</x:v>
-      </x:c>
-      <x:c r="K12" s="32" t="n">
-        <x:f>IF(J12="","",(1/'Metadata'!$B$5)^(J12-1))</x:f>
-        <x:v>2839.798248160936</x:v>
-      </x:c>
-      <x:c r="L12" s="31" t="n">
-        <x:f>IF(E12=0,"",E12*K12)</x:f>
+        <x:f>IF(B12=0,"",B12*D12)</x:f>
         <x:v>4304160.020569195</x:v>
-      </x:c>
-      <x:c r="M12" s="31" t="n">
-        <x:f>IF(E12=0,"",I12-L12)</x:f>
-        <x:v>42660.36170387268</x:v>
-      </x:c>
-      <x:c r="N12" s="32" t="n">
-        <x:f>IF(L12=0,"",I12/L12)</x:f>
-        <x:v>1.0099114255743287</x:v>
-      </x:c>
-      <x:c r="O12" s="34" t="n">
-        <x:f>IF(L12=0,"",M12/L12)</x:f>
-        <x:v>0.009911425574328704</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="18" customHeight="1">
       <x:c r="A13" s="24" t="str">
         <x:v>Medium bathypelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B13" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C13" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D13" s="31" t="n">
+      <x:c r="B13" s="31" t="n">
         <x:v>0.3530681481</x:v>
       </x:c>
+      <x:c r="C13" s="32" t="n">
+        <x:v>4.08</x:v>
+      </x:c>
+      <x:c r="D13" s="32" t="n">
+        <x:f>IF(C13="","",(1/'Metadata'!$B$5)^(C13-1))</x:f>
+        <x:v>1202.2644346174131</x:v>
+      </x:c>
       <x:c r="E13" s="31" t="n">
-        <x:v>0.3530681481</x:v>
-      </x:c>
-      <x:c r="F13" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G13" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H13" s="32" t="n">
-        <x:f>IF(E13=0,"",I13/E13)</x:f>
-        <x:v>1202.2644346174131</x:v>
-      </x:c>
-      <x:c r="I13" s="31" t="n">
-        <x:f>IF(C13=0,"",SUMIF('Species'!$G$2:$G$160,A13,'Species'!$U$2:$U$160))</x:f>
+        <x:f>IF(B13=0,"",B13*D13)</x:f>
         <x:v>424.48127745686355</x:v>
-      </x:c>
-      <x:c r="J13" s="32" t="n">
-        <x:v>4.08</x:v>
-      </x:c>
-      <x:c r="K13" s="32" t="n">
-        <x:f>IF(J13="","",(1/'Metadata'!$B$5)^(J13-1))</x:f>
-        <x:v>1202.2644346174131</x:v>
-      </x:c>
-      <x:c r="L13" s="31" t="n">
-        <x:f>IF(E13=0,"",E13*K13)</x:f>
-        <x:v>424.48127745686355</x:v>
-      </x:c>
-      <x:c r="M13" s="31" t="n">
-        <x:f>IF(E13=0,"",I13-L13)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N13" s="32" t="n">
-        <x:f>IF(L13=0,"",I13/L13)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O13" s="34" t="n">
-        <x:f>IF(L13=0,"",M13/L13)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="18" customHeight="1">
       <x:c r="A14" s="24" t="str">
         <x:v>Medium benthopelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B14" s="33" t="n">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="C14" s="33" t="n">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="D14" s="31" t="n">
+      <x:c r="B14" s="31" t="n">
         <x:v>4619.115086357499</x:v>
       </x:c>
+      <x:c r="C14" s="32" t="n">
+        <x:v>3.5255423330227864</x:v>
+      </x:c>
+      <x:c r="D14" s="32" t="n">
+        <x:f>IF(C14="","",(1/'Metadata'!$B$5)^(C14-1))</x:f>
+        <x:v>335.3839945420269</x:v>
+      </x:c>
       <x:c r="E14" s="31" t="n">
-        <x:v>4619.115086357499</x:v>
-      </x:c>
-      <x:c r="F14" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G14" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H14" s="32" t="n">
-        <x:f>IF(E14=0,"",I14/E14)</x:f>
-        <x:v>465.37554898844365</x:v>
-      </x:c>
-      <x:c r="I14" s="31" t="n">
-        <x:f>IF(C14=0,"",SUMIF('Species'!$G$2:$G$160,A14,'Species'!$U$2:$U$160))</x:f>
-        <x:v>2149623.2191544236</x:v>
-      </x:c>
-      <x:c r="J14" s="32" t="n">
-        <x:v>3.5255423330227864</x:v>
-      </x:c>
-      <x:c r="K14" s="32" t="n">
-        <x:f>IF(J14="","",(1/'Metadata'!$B$5)^(J14-1))</x:f>
-        <x:v>335.3839945420269</x:v>
-      </x:c>
-      <x:c r="L14" s="31" t="n">
-        <x:f>IF(E14=0,"",E14*K14)</x:f>
+        <x:f>IF(B14=0,"",B14*D14)</x:f>
         <x:v>1549177.268911918</x:v>
-      </x:c>
-      <x:c r="M14" s="31" t="n">
-        <x:f>IF(E14=0,"",I14-L14)</x:f>
-        <x:v>600445.9502425056</x:v>
-      </x:c>
-      <x:c r="N14" s="32" t="n">
-        <x:f>IF(L14=0,"",I14/L14)</x:f>
-        <x:v>1.3875902146848795</x:v>
-      </x:c>
-      <x:c r="O14" s="34" t="n">
-        <x:f>IF(L14=0,"",M14/L14)</x:f>
-        <x:v>0.38759021468487953</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="18" customHeight="1">
       <x:c r="A15" s="24" t="str">
         <x:v>Medium demersals (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B15" s="33" t="n">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="C15" s="33" t="n">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="D15" s="31" t="n">
+      <x:c r="B15" s="31" t="n">
         <x:v>10954.865029215402</x:v>
       </x:c>
+      <x:c r="C15" s="32" t="n">
+        <x:v>3.4813059841397997</x:v>
+      </x:c>
+      <x:c r="D15" s="32" t="n">
+        <x:f>IF(C15="","",(1/'Metadata'!$B$5)^(C15-1))</x:f>
+        <x:v>302.9046805087631</x:v>
+      </x:c>
       <x:c r="E15" s="31" t="n">
-        <x:v>10954.865029215402</x:v>
-      </x:c>
-      <x:c r="F15" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G15" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H15" s="32" t="n">
-        <x:f>IF(E15=0,"",I15/E15)</x:f>
-        <x:v>387.6374743545324</x:v>
-      </x:c>
-      <x:c r="I15" s="31" t="n">
-        <x:f>IF(C15=0,"",SUMIF('Species'!$G$2:$G$160,A15,'Species'!$U$2:$U$160))</x:f>
-        <x:v>4246516.211819849</x:v>
-      </x:c>
-      <x:c r="J15" s="32" t="n">
-        <x:v>3.4813059841397997</x:v>
-      </x:c>
-      <x:c r="K15" s="32" t="n">
-        <x:f>IF(J15="","",(1/'Metadata'!$B$5)^(J15-1))</x:f>
-        <x:v>302.9046805087631</x:v>
-      </x:c>
-      <x:c r="L15" s="31" t="n">
-        <x:f>IF(E15=0,"",E15*K15)</x:f>
+        <x:f>IF(B15=0,"",B15*D15)</x:f>
         <x:v>3318279.891691113</x:v>
-      </x:c>
-      <x:c r="M15" s="31" t="n">
-        <x:f>IF(E15=0,"",I15-L15)</x:f>
-        <x:v>928236.3201287361</x:v>
-      </x:c>
-      <x:c r="N15" s="32" t="n">
-        <x:f>IF(L15=0,"",I15/L15)</x:f>
-        <x:v>1.2797341847060628</x:v>
-      </x:c>
-      <x:c r="O15" s="34" t="n">
-        <x:f>IF(L15=0,"",M15/L15)</x:f>
-        <x:v>0.27973418470606287</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="18" customHeight="1">
       <x:c r="A16" s="24" t="str">
         <x:v>Medium pelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B16" s="33" t="n">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C16" s="33" t="n">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="D16" s="31" t="n">
+      <x:c r="B16" s="31" t="n">
         <x:v>5964.653578957001</x:v>
       </x:c>
+      <x:c r="C16" s="32" t="n">
+        <x:v>3.8137572676616753</x:v>
+      </x:c>
+      <x:c r="D16" s="32" t="n">
+        <x:f>IF(C16="","",(1/'Metadata'!$B$5)^(C16-1))</x:f>
+        <x:v>651.264292980289</x:v>
+      </x:c>
       <x:c r="E16" s="31" t="n">
-        <x:v>5964.653578957001</x:v>
-      </x:c>
-      <x:c r="F16" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G16" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H16" s="32" t="n">
-        <x:f>IF(E16=0,"",I16/E16)</x:f>
-        <x:v>845.2201814928917</x:v>
-      </x:c>
-      <x:c r="I16" s="31" t="n">
-        <x:f>IF(C16=0,"",SUMIF('Species'!$G$2:$G$160,A16,'Species'!$U$2:$U$160))</x:f>
-        <x:v>5041445.580548262</x:v>
-      </x:c>
-      <x:c r="J16" s="32" t="n">
-        <x:v>3.8137572676616753</x:v>
-      </x:c>
-      <x:c r="K16" s="32" t="n">
-        <x:f>IF(J16="","",(1/'Metadata'!$B$5)^(J16-1))</x:f>
-        <x:v>651.264292980289</x:v>
-      </x:c>
-      <x:c r="L16" s="31" t="n">
-        <x:f>IF(E16=0,"",E16*K16)</x:f>
+        <x:f>IF(B16=0,"",B16*D16)</x:f>
         <x:v>3884565.8959717816</x:v>
-      </x:c>
-      <x:c r="M16" s="31" t="n">
-        <x:f>IF(E16=0,"",I16-L16)</x:f>
-        <x:v>1156879.6845764806</x:v>
-      </x:c>
-      <x:c r="N16" s="32" t="n">
-        <x:f>IF(L16=0,"",I16/L16)</x:f>
-        <x:v>1.2978144059227164</x:v>
-      </x:c>
-      <x:c r="O16" s="34" t="n">
-        <x:f>IF(L16=0,"",M16/L16)</x:f>
-        <x:v>0.2978144059227164</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="18" customHeight="1">
       <x:c r="A17" s="24" t="str">
         <x:v>Medium reef assoc. fish (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B17" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C17" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D17" s="31" t="n">
+      <x:c r="B17" s="31" t="n">
         <x:v>3071.5417734644</x:v>
       </x:c>
+      <x:c r="C17" s="32" t="n">
+        <x:v>3.3852207320123555</x:v>
+      </x:c>
+      <x:c r="D17" s="32" t="n">
+        <x:f>IF(C17="","",(1/'Metadata'!$B$5)^(C17-1))</x:f>
+        <x:v>242.78437434319176</x:v>
+      </x:c>
       <x:c r="E17" s="31" t="n">
-        <x:v>3071.5417734644</x:v>
-      </x:c>
-      <x:c r="F17" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G17" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H17" s="32" t="n">
-        <x:f>IF(E17=0,"",I17/E17)</x:f>
-        <x:v>507.10028869969744</x:v>
-      </x:c>
-      <x:c r="I17" s="31" t="n">
-        <x:f>IF(C17=0,"",SUMIF('Species'!$G$2:$G$160,A17,'Species'!$U$2:$U$160))</x:f>
-        <x:v>1557579.720076978</x:v>
-      </x:c>
-      <x:c r="J17" s="32" t="n">
-        <x:v>3.3852207320123555</x:v>
-      </x:c>
-      <x:c r="K17" s="32" t="n">
-        <x:f>IF(J17="","",(1/'Metadata'!$B$5)^(J17-1))</x:f>
-        <x:v>242.78437434319176</x:v>
-      </x:c>
-      <x:c r="L17" s="31" t="n">
-        <x:f>IF(E17=0,"",E17*K17)</x:f>
+        <x:f>IF(B17=0,"",B17*D17)</x:f>
         <x:v>745722.347739532</x:v>
-      </x:c>
-      <x:c r="M17" s="31" t="n">
-        <x:f>IF(E17=0,"",I17-L17)</x:f>
-        <x:v>811857.372337446</x:v>
-      </x:c>
-      <x:c r="N17" s="32" t="n">
-        <x:f>IF(L17=0,"",I17/L17)</x:f>
-        <x:v>2.0886858557992602</x:v>
-      </x:c>
-      <x:c r="O17" s="34" t="n">
-        <x:f>IF(L17=0,"",M17/L17)</x:f>
-        <x:v>1.0886858557992602</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="18" customHeight="1">
       <x:c r="A18" s="24" t="str">
         <x:v>Other demersal invertebrates</x:v>
       </x:c>
-      <x:c r="B18" s="33" t="n">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C18" s="33" t="n">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="D18" s="31" t="n">
+      <x:c r="B18" s="31" t="n">
         <x:v>1625.0153135075</x:v>
       </x:c>
+      <x:c r="C18" s="32" t="n">
+        <x:v>2.6507931335344135</x:v>
+      </x:c>
+      <x:c r="D18" s="32" t="n">
+        <x:f>IF(C18="","",(1/'Metadata'!$B$5)^(C18-1))</x:f>
+        <x:v>44.75000967371618</x:v>
+      </x:c>
       <x:c r="E18" s="31" t="n">
-        <x:v>1625.0153135075</x:v>
-      </x:c>
-      <x:c r="F18" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G18" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H18" s="32" t="n">
-        <x:f>IF(E18=0,"",I18/E18)</x:f>
-        <x:v>65.47312239614492</x:v>
-      </x:c>
-      <x:c r="I18" s="31" t="n">
-        <x:f>IF(C18=0,"",SUMIF('Species'!$G$2:$G$160,A18,'Species'!$U$2:$U$160))</x:f>
-        <x:v>106394.82651688634</x:v>
-      </x:c>
-      <x:c r="J18" s="32" t="n">
-        <x:v>2.6507931335344135</x:v>
-      </x:c>
-      <x:c r="K18" s="32" t="n">
-        <x:f>IF(J18="","",(1/'Metadata'!$B$5)^(J18-1))</x:f>
-        <x:v>44.75000967371618</x:v>
-      </x:c>
-      <x:c r="L18" s="31" t="n">
-        <x:f>IF(E18=0,"",E18*K18)</x:f>
+        <x:f>IF(B18=0,"",B18*D18)</x:f>
         <x:v>72719.45099939755</x:v>
-      </x:c>
-      <x:c r="M18" s="31" t="n">
-        <x:f>IF(E18=0,"",I18-L18)</x:f>
-        <x:v>33675.37551748879</x:v>
-      </x:c>
-      <x:c r="N18" s="32" t="n">
-        <x:f>IF(L18=0,"",I18/L18)</x:f>
-        <x:v>1.4630862177131643</x:v>
-      </x:c>
-      <x:c r="O18" s="34" t="n">
-        <x:f>IF(L18=0,"",M18/L18)</x:f>
-        <x:v>0.4630862177131642</x:v>
       </x:c>
     </x:row>
     <x:row r="19" ht="18" customHeight="1">
       <x:c r="A19" s="24" t="str">
         <x:v>Shrimps</x:v>
       </x:c>
-      <x:c r="B19" s="33" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="C19" s="33" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="D19" s="31" t="n">
+      <x:c r="B19" s="31" t="n">
         <x:v>421.29403639500003</x:v>
       </x:c>
+      <x:c r="C19" s="32" t="n">
+        <x:v>3.107860364599147</x:v>
+      </x:c>
+      <x:c r="D19" s="32" t="n">
+        <x:f>IF(C19="","",(1/'Metadata'!$B$5)^(C19-1))</x:f>
+        <x:v>128.19183509335792</x:v>
+      </x:c>
       <x:c r="E19" s="31" t="n">
-        <x:v>421.29403639500003</x:v>
-      </x:c>
-      <x:c r="F19" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G19" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H19" s="32" t="n">
-        <x:f>IF(E19=0,"",I19/E19)</x:f>
-        <x:v>202.21589338929292</x:v>
-      </x:c>
-      <x:c r="I19" s="31" t="n">
-        <x:f>IF(C19=0,"",SUMIF('Species'!$G$2:$G$160,A19,'Species'!$U$2:$U$160))</x:f>
-        <x:v>85192.34994919621</x:v>
-      </x:c>
-      <x:c r="J19" s="32" t="n">
-        <x:v>3.107860364599147</x:v>
-      </x:c>
-      <x:c r="K19" s="32" t="n">
-        <x:f>IF(J19="","",(1/'Metadata'!$B$5)^(J19-1))</x:f>
-        <x:v>128.19183509335792</x:v>
-      </x:c>
-      <x:c r="L19" s="31" t="n">
-        <x:f>IF(E19=0,"",E19*K19)</x:f>
+        <x:f>IF(B19=0,"",B19*D19)</x:f>
         <x:v>54006.455639362975</x:v>
-      </x:c>
-      <x:c r="M19" s="31" t="n">
-        <x:f>IF(E19=0,"",I19-L19)</x:f>
-        <x:v>31185.89430983324</x:v>
-      </x:c>
-      <x:c r="N19" s="32" t="n">
-        <x:f>IF(L19=0,"",I19/L19)</x:f>
-        <x:v>1.5774475280896454</x:v>
-      </x:c>
-      <x:c r="O19" s="34" t="n">
-        <x:f>IF(L19=0,"",M19/L19)</x:f>
-        <x:v>0.5774475280896454</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="18" customHeight="1">
       <x:c r="A20" s="24" t="str">
         <x:v>Small benthopelagics (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B20" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C20" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D20" s="31" t="n">
+      <x:c r="B20" s="31" t="n">
         <x:v>15.622664259299999</x:v>
       </x:c>
+      <x:c r="C20" s="32" t="n">
+        <x:v>3.5496058519400537</x:v>
+      </x:c>
+      <x:c r="D20" s="32" t="n">
+        <x:f>IF(C20="","",(1/'Metadata'!$B$5)^(C20-1))</x:f>
+        <x:v>354.49152106949964</x:v>
+      </x:c>
       <x:c r="E20" s="31" t="n">
-        <x:v>15.622664259299999</x:v>
-      </x:c>
-      <x:c r="F20" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G20" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H20" s="32" t="n">
-        <x:f>IF(E20=0,"",I20/E20)</x:f>
-        <x:v>368.1526362219499</x:v>
-      </x:c>
-      <x:c r="I20" s="31" t="n">
-        <x:f>IF(C20=0,"",SUMIF('Species'!$G$2:$G$160,A20,'Species'!$U$2:$U$160))</x:f>
-        <x:v>5751.525031871731</x:v>
-      </x:c>
-      <x:c r="J20" s="32" t="n">
-        <x:v>3.5496058519400537</x:v>
-      </x:c>
-      <x:c r="K20" s="32" t="n">
-        <x:f>IF(J20="","",(1/'Metadata'!$B$5)^(J20-1))</x:f>
-        <x:v>354.49152106949964</x:v>
-      </x:c>
-      <x:c r="L20" s="31" t="n">
-        <x:f>IF(E20=0,"",E20*K20)</x:f>
+        <x:f>IF(B20=0,"",B20*D20)</x:f>
         <x:v>5538.102016437365</x:v>
-      </x:c>
-      <x:c r="M20" s="31" t="n">
-        <x:f>IF(E20=0,"",I20-L20)</x:f>
-        <x:v>213.42301543436588</x:v>
-      </x:c>
-      <x:c r="N20" s="32" t="n">
-        <x:f>IF(L20=0,"",I20/L20)</x:f>
-        <x:v>1.038537212713113</x:v>
-      </x:c>
-      <x:c r="O20" s="34" t="n">
-        <x:f>IF(L20=0,"",M20/L20)</x:f>
-        <x:v>0.03853721271311284</x:v>
       </x:c>
     </x:row>
     <x:row r="21" ht="18" customHeight="1">
       <x:c r="A21" s="24" t="str">
         <x:v>Small demersals (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B21" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C21" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D21" s="31" t="n">
+      <x:c r="B21" s="31" t="n">
         <x:v>44.3745315382</x:v>
       </x:c>
+      <x:c r="C21" s="32" t="n">
+        <x:v>3.5800000000000005</x:v>
+      </x:c>
+      <x:c r="D21" s="32" t="n">
+        <x:f>IF(C21="","",(1/'Metadata'!$B$5)^(C21-1))</x:f>
+        <x:v>380.1893963205616</x:v>
+      </x:c>
       <x:c r="E21" s="31" t="n">
-        <x:v>44.3745315382</x:v>
-      </x:c>
-      <x:c r="F21" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G21" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H21" s="32" t="n">
-        <x:f>IF(E21=0,"",I21/E21)</x:f>
-        <x:v>380.1893963205613</x:v>
-      </x:c>
-      <x:c r="I21" s="31" t="n">
-        <x:f>IF(C21=0,"",SUMIF('Species'!$G$2:$G$160,A21,'Species'!$U$2:$U$160))</x:f>
-        <x:v>16870.726357515967</x:v>
-      </x:c>
-      <x:c r="J21" s="32" t="n">
-        <x:v>3.5800000000000005</x:v>
-      </x:c>
-      <x:c r="K21" s="32" t="n">
-        <x:f>IF(J21="","",(1/'Metadata'!$B$5)^(J21-1))</x:f>
-        <x:v>380.1893963205616</x:v>
-      </x:c>
-      <x:c r="L21" s="31" t="n">
-        <x:f>IF(E21=0,"",E21*K21)</x:f>
+        <x:f>IF(B21=0,"",B21*D21)</x:f>
         <x:v>16870.72635751598</x:v>
-      </x:c>
-      <x:c r="M21" s="31" t="n">
-        <x:f>IF(E21=0,"",I21-L21)</x:f>
-        <x:v>-1.4551915228366852e-11</x:v>
-      </x:c>
-      <x:c r="N21" s="32" t="n">
-        <x:f>IF(L21=0,"",I21/L21)</x:f>
-        <x:v>0.9999999999999991</x:v>
-      </x:c>
-      <x:c r="O21" s="34" t="n">
-        <x:f>IF(L21=0,"",M21/L21)</x:f>
-        <x:v>-8.625541615689778e-16</x:v>
       </x:c>
     </x:row>
     <x:row r="22" ht="18" customHeight="1">
       <x:c r="A22" s="24" t="str">
         <x:v>Small pelagics (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B22" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="C22" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="D22" s="31" t="n">
+      <x:c r="B22" s="31" t="n">
         <x:v>5823.338386621501</x:v>
       </x:c>
+      <x:c r="C22" s="32" t="n">
+        <x:v>3.100051746009127</x:v>
+      </x:c>
+      <x:c r="D22" s="32" t="n">
+        <x:f>IF(C22="","",(1/'Metadata'!$B$5)^(C22-1))</x:f>
+        <x:v>125.90754211764643</x:v>
+      </x:c>
       <x:c r="E22" s="31" t="n">
-        <x:v>5823.338386621501</x:v>
-      </x:c>
-      <x:c r="F22" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G22" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H22" s="32" t="n">
-        <x:f>IF(E22=0,"",I22/E22)</x:f>
-        <x:v>126.17759896492245</x:v>
-      </x:c>
-      <x:c r="I22" s="31" t="n">
-        <x:f>IF(C22=0,"",SUMIF('Species'!$G$2:$G$160,A22,'Species'!$U$2:$U$160))</x:f>
-        <x:v>734774.8555841662</x:v>
-      </x:c>
-      <x:c r="J22" s="32" t="n">
-        <x:v>3.100051746009127</x:v>
-      </x:c>
-      <x:c r="K22" s="32" t="n">
-        <x:f>IF(J22="","",(1/'Metadata'!$B$5)^(J22-1))</x:f>
-        <x:v>125.90754211764643</x:v>
-      </x:c>
-      <x:c r="L22" s="31" t="n">
-        <x:f>IF(E22=0,"",E22*K22)</x:f>
+        <x:f>IF(B22=0,"",B22*D22)</x:f>
         <x:v>733202.2231788539</x:v>
-      </x:c>
-      <x:c r="M22" s="31" t="n">
-        <x:f>IF(E22=0,"",I22-L22)</x:f>
-        <x:v>1572.6324053123826</x:v>
-      </x:c>
-      <x:c r="N22" s="32" t="n">
-        <x:f>IF(L22=0,"",I22/L22)</x:f>
-        <x:v>1.0021448822106596</x:v>
-      </x:c>
-      <x:c r="O22" s="34" t="n">
-        <x:f>IF(L22=0,"",M22/L22)</x:f>
-        <x:v>0.002144882210659585</x:v>
       </x:c>
     </x:row>
     <x:row r="23" ht="18" customHeight="1">
       <x:c r="A23" s="24" t="str">
         <x:v>Small reef assoc. fish (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B23" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C23" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D23" s="31" t="n">
+      <x:c r="B23" s="31" t="n">
         <x:v>97.6404007128</x:v>
       </x:c>
+      <x:c r="C23" s="32" t="n">
+        <x:v>3.11</x:v>
+      </x:c>
+      <x:c r="D23" s="32" t="n">
+        <x:f>IF(C23="","",(1/'Metadata'!$B$5)^(C23-1))</x:f>
+        <x:v>128.82495516931337</x:v>
+      </x:c>
       <x:c r="E23" s="31" t="n">
-        <x:v>97.6404007128</x:v>
-      </x:c>
-      <x:c r="F23" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G23" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H23" s="32" t="n">
-        <x:f>IF(E23=0,"",I23/E23)</x:f>
-        <x:v>128.82495516931337</x:v>
-      </x:c>
-      <x:c r="I23" s="31" t="n">
-        <x:f>IF(C23=0,"",SUMIF('Species'!$G$2:$G$160,A23,'Species'!$U$2:$U$160))</x:f>
+        <x:f>IF(B23=0,"",B23*D23)</x:f>
         <x:v>12578.520244540254</x:v>
-      </x:c>
-      <x:c r="J23" s="32" t="n">
-        <x:v>3.11</x:v>
-      </x:c>
-      <x:c r="K23" s="32" t="n">
-        <x:f>IF(J23="","",(1/'Metadata'!$B$5)^(J23-1))</x:f>
-        <x:v>128.82495516931337</x:v>
-      </x:c>
-      <x:c r="L23" s="31" t="n">
-        <x:f>IF(E23=0,"",E23*K23)</x:f>
-        <x:v>12578.520244540254</x:v>
-      </x:c>
-      <x:c r="M23" s="31" t="n">
-        <x:f>IF(E23=0,"",I23-L23)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N23" s="32" t="n">
-        <x:f>IF(L23=0,"",I23/L23)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O23" s="34" t="n">
-        <x:f>IF(L23=0,"",M23/L23)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="24" ht="18" customHeight="1">
       <x:c r="A24" s="24" t="str">
         <x:v>Small to medium flatfishes (&lt;90 cm)</x:v>
       </x:c>
-      <x:c r="B24" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="C24" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="D24" s="31" t="n">
+      <x:c r="B24" s="31" t="n">
         <x:v>687.3498312336001</x:v>
       </x:c>
+      <x:c r="C24" s="32" t="n">
+        <x:v>3.5850554913198467</x:v>
+      </x:c>
+      <x:c r="D24" s="32" t="n">
+        <x:f>IF(C24="","",(1/'Metadata'!$B$5)^(C24-1))</x:f>
+        <x:v>384.64092581755096</x:v>
+      </x:c>
       <x:c r="E24" s="31" t="n">
-        <x:v>687.3498312336001</x:v>
-      </x:c>
-      <x:c r="F24" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G24" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H24" s="32" t="n">
-        <x:f>IF(E24=0,"",I24/E24)</x:f>
-        <x:v>840.2056031969029</x:v>
-      </x:c>
-      <x:c r="I24" s="31" t="n">
-        <x:f>IF(C24=0,"",SUMIF('Species'!$G$2:$G$160,A24,'Species'!$U$2:$U$160))</x:f>
-        <x:v>577515.1795589164</x:v>
-      </x:c>
-      <x:c r="J24" s="32" t="n">
-        <x:v>3.5850554913198467</x:v>
-      </x:c>
-      <x:c r="K24" s="32" t="n">
-        <x:f>IF(J24="","",(1/'Metadata'!$B$5)^(J24-1))</x:f>
-        <x:v>384.64092581755096</x:v>
-      </x:c>
-      <x:c r="L24" s="31" t="n">
-        <x:f>IF(E24=0,"",E24*K24)</x:f>
+        <x:f>IF(B24=0,"",B24*D24)</x:f>
         <x:v>264382.87544622936</x:v>
-      </x:c>
-      <x:c r="M24" s="31" t="n">
-        <x:f>IF(E24=0,"",I24-L24)</x:f>
-        <x:v>313132.304112687</x:v>
-      </x:c>
-      <x:c r="N24" s="32" t="n">
-        <x:f>IF(L24=0,"",I24/L24)</x:f>
-        <x:v>2.184389509283374</x:v>
-      </x:c>
-      <x:c r="O24" s="34" t="n">
-        <x:f>IF(L24=0,"",M24/L24)</x:f>
-        <x:v>1.184389509283374</x:v>
       </x:c>
     </x:row>
     <x:row r="25" ht="18" customHeight="1">
       <x:c r="A25" s="24" t="str">
         <x:v>Small to medium rays (&lt;90 cm)</x:v>
       </x:c>
-      <x:c r="B25" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C25" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D25" s="31" t="n">
+      <x:c r="B25" s="31" t="n">
         <x:v>220.6169293974</x:v>
       </x:c>
+      <x:c r="C25" s="32" t="n">
+        <x:v>3.8562768993238112</x:v>
+      </x:c>
+      <x:c r="D25" s="32" t="n">
+        <x:f>IF(C25="","",(1/'Metadata'!$B$5)^(C25-1))</x:f>
+        <x:v>718.2520915376099</x:v>
+      </x:c>
       <x:c r="E25" s="31" t="n">
-        <x:v>220.6169293974</x:v>
-      </x:c>
-      <x:c r="F25" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G25" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H25" s="32" t="n">
-        <x:f>IF(E25=0,"",I25/E25)</x:f>
-        <x:v>807.2062931561243</x:v>
-      </x:c>
-      <x:c r="I25" s="31" t="n">
-        <x:f>IF(C25=0,"",SUMIF('Species'!$G$2:$G$160,A25,'Species'!$U$2:$U$160))</x:f>
-        <x:v>178083.37378636166</x:v>
-      </x:c>
-      <x:c r="J25" s="32" t="n">
-        <x:v>3.8562768993238112</x:v>
-      </x:c>
-      <x:c r="K25" s="32" t="n">
-        <x:f>IF(J25="","",(1/'Metadata'!$B$5)^(J25-1))</x:f>
-        <x:v>718.2520915376099</x:v>
-      </x:c>
-      <x:c r="L25" s="31" t="n">
-        <x:f>IF(E25=0,"",E25*K25)</x:f>
+        <x:f>IF(B25=0,"",B25*D25)</x:f>
         <x:v>158458.57096828776</x:v>
-      </x:c>
-      <x:c r="M25" s="31" t="n">
-        <x:f>IF(E25=0,"",I25-L25)</x:f>
-        <x:v>19624.80281807389</x:v>
-      </x:c>
-      <x:c r="N25" s="32" t="n">
-        <x:f>IF(L25=0,"",I25/L25)</x:f>
-        <x:v>1.1238481623187262</x:v>
-      </x:c>
-      <x:c r="O25" s="34" t="n">
-        <x:f>IF(L25=0,"",M25/L25)</x:f>
-        <x:v>0.12384816231872615</x:v>
       </x:c>
     </x:row>
     <x:row r="26" ht="18" customHeight="1">
       <x:c r="A26" s="24" t="str">
         <x:v>Small to medium sharks (&lt;90 cm)</x:v>
       </x:c>
-      <x:c r="B26" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C26" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D26" s="31" t="n">
+      <x:c r="B26" s="31" t="n">
         <x:v>89.8843424585</x:v>
       </x:c>
+      <x:c r="C26" s="32" t="n">
+        <x:v>3.8232102615798427</x:v>
+      </x:c>
+      <x:c r="D26" s="32" t="n">
+        <x:f>IF(C26="","",(1/'Metadata'!$B$5)^(C26-1))</x:f>
+        <x:v>665.5953229747363</x:v>
+      </x:c>
       <x:c r="E26" s="31" t="n">
-        <x:v>89.8843424585</x:v>
-      </x:c>
-      <x:c r="F26" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G26" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H26" s="32" t="n">
-        <x:f>IF(E26=0,"",I26/E26)</x:f>
-        <x:v>665.8092014449121</x:v>
-      </x:c>
-      <x:c r="I26" s="31" t="n">
-        <x:f>IF(C26=0,"",SUMIF('Species'!$G$2:$G$160,A26,'Species'!$U$2:$U$160))</x:f>
-        <x:v>59845.82227469489</x:v>
-      </x:c>
-      <x:c r="J26" s="32" t="n">
-        <x:v>3.8232102615798427</x:v>
-      </x:c>
-      <x:c r="K26" s="32" t="n">
-        <x:f>IF(J26="","",(1/'Metadata'!$B$5)^(J26-1))</x:f>
-        <x:v>665.5953229747363</x:v>
-      </x:c>
-      <x:c r="L26" s="31" t="n">
-        <x:f>IF(E26=0,"",E26*K26)</x:f>
+        <x:f>IF(B26=0,"",B26*D26)</x:f>
         <x:v>59826.59794903711</x:v>
       </x:c>
-      <x:c r="M26" s="31" t="n">
-        <x:f>IF(E26=0,"",I26-L26)</x:f>
-        <x:v>19.224325657778536</x:v>
-      </x:c>
-      <x:c r="N26" s="32" t="n">
-        <x:f>IF(L26=0,"",I26/L26)</x:f>
-        <x:v>1.0003213340941457</x:v>
-      </x:c>
-      <x:c r="O26" s="34" t="n">
-        <x:f>IF(L26=0,"",M26/L26)</x:f>
-        <x:v>0.0003213340941457953</x:v>
-      </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="G2:G26">
-    <x:cfRule type="cellIs" dxfId="2" priority="1" operator="lessThan">
-      <x:formula>0.9</x:formula>
-    </x:cfRule>
-  </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="O2:O26">
-    <x:cfRule type="dataBar" priority="2">
-      <x:dataBar>
-        <x:cfvo type="min"/>
-        <x:cfvo type="max"/>
-        <x:color rgb="FFE28A32"/>
-      </x:dataBar>
-    </x:cfRule>
-  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R737b8a2771974c76"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3a26fdc5a54c4a8f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -13700,7 +12251,7 @@
       <x:c r="B5" s="24" t="str">
         <x:v>catch_reconciled</x:v>
       </x:c>
-      <x:c r="C5" s="35" t="b">
+      <x:c r="C5" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D5" s="24" t="str">
@@ -13799,7 +12350,7 @@
         <x:v>commercial_ppr</x:v>
       </x:c>
       <x:c r="C12" s="24" t="n">
-        <x:v>38061004.15079787</x:v>
+        <x:v>27105688.547792196</x:v>
       </x:c>
       <x:c r="D12" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -13813,7 +12364,7 @@
         <x:v>functional_ppr</x:v>
       </x:c>
       <x:c r="C13" s="24" t="n">
-        <x:v>38061004.150797874</x:v>
+        <x:v>31381596.30210026</x:v>
       </x:c>
       <x:c r="D13" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -13827,7 +12378,7 @@
         <x:v>commercial_ppr_difference</x:v>
       </x:c>
       <x:c r="C14" s="24" t="n">
-        <x:v>-7.450580596923828e-9</x:v>
+        <x:v>-10955315.603005677</x:v>
       </x:c>
       <x:c r="D14" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -13841,7 +12392,7 @@
         <x:v>functional_ppr_difference</x:v>
       </x:c>
       <x:c r="C15" s="24" t="n">
-        <x:v>0</x:v>
+        <x:v>-6679407.848697614</x:v>
       </x:c>
       <x:c r="D15" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -13852,9 +12403,9 @@
         <x:v>EEZ_918</x:v>
       </x:c>
       <x:c r="B16" s="24" t="str">
-        <x:v>commercial_ppr_reconciled</x:v>
-      </x:c>
-      <x:c r="C16" s="35" t="b">
+        <x:v>tl_coverage_complete</x:v>
+      </x:c>
+      <x:c r="C16" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D16" s="24" t="str">
@@ -13866,47 +12417,19 @@
         <x:v>EEZ_918</x:v>
       </x:c>
       <x:c r="B17" s="24" t="str">
-        <x:v>functional_ppr_reconciled</x:v>
-      </x:c>
-      <x:c r="C17" s="35" t="b">
+        <x:v>group_ppr_within_convexity_bound</x:v>
+      </x:c>
+      <x:c r="C17" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D17" s="24" t="str">
         <x:v>boolean</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" ht="18" customHeight="1">
-      <x:c r="A18" s="24" t="str">
-        <x:v>EEZ_918</x:v>
-      </x:c>
-      <x:c r="B18" s="24" t="str">
-        <x:v>commercial_jensen_violations</x:v>
-      </x:c>
-      <x:c r="C18" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D18" s="24" t="str">
-        <x:v>count</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" ht="18" customHeight="1">
-      <x:c r="A19" s="24" t="str">
-        <x:v>EEZ_918</x:v>
-      </x:c>
-      <x:c r="B19" s="24" t="str">
-        <x:v>functional_jensen_violations</x:v>
-      </x:c>
-      <x:c r="C19" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D19" s="24" t="str">
-        <x:v>count</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re8bbb0df6f1a49de"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9c8fb60b329a4d92"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -13953,7 +12476,7 @@
       <x:c r="A5" s="22" t="str">
         <x:v>Transfer efficiency</x:v>
       </x:c>
-      <x:c r="B5" s="36" t="n">
+      <x:c r="B5" s="34" t="n">
         <x:v>0.1</x:v>
       </x:c>
       <x:c r="C5" s="18" t="str">
